--- a/buffett_value_stocks.xlsx
+++ b/buffett_value_stocks.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +63,12 @@
     <font>
       <name val="微軟正黑體"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <color rgb="000984e3"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="微軟正黑體"/>
@@ -178,7 +184,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,19 +199,19 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,9 +226,6 @@
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -232,10 +235,13 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -250,22 +256,22 @@
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -280,21 +286,21 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -688,7 +694,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>資料: 2026 Q1 財報 + 2026-07-16 行情 | 產出: 2026-10-04 00:24</t>
+          <t>資料: 2026 Q1 財報 + 2026-07-16 行情 | 產出: 2026-10-04 06:22</t>
         </is>
       </c>
     </row>
@@ -44452,6 +44458,1090 @@
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B169" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B175" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B177" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B178" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B179" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B180" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B181" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B182" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B183" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B184" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B185" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B187" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B188" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B189" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B190" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B192" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B193" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B194" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B195" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B196" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B197" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B199" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B200" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B201" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B202" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B203" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B205" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B206" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B207" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B208" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B209" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B210" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B211" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B212" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B213" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B214" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B215" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B216" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B217" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B218" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B219" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B220" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B221" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B222" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B223" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B224" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B225" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B226" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B227" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B228" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B229" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B230" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B231" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B232" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B233" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B234" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B235" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B236" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B237" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B238" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B239" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B240" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B241" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B242" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B243" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B244" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B245" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B246" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B247" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B248" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B249" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B250" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B251" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B252" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B253" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B254" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B255" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B256" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B257" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B258" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B259" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B260" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B261" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B262" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B263" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B264" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B265" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B266" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B267" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B268" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B269" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B270" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B271" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B272" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B273" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B274" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B275" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B276" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B277" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B278" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B279" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B280" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B281" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B282" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B283" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B284" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B285" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B286" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B287" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B288" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B289" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B290" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B291" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B292" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B293" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B294" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B295" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B296" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B297" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B298" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B299" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B300" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B301" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B302" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B303" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B304" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B305" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B306" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B307" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B308" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B309" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B310" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B311" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B312" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B313" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B314" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B315" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B316" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B317" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B318" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B319" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B320" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B321" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B322" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B323" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B324" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B325" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B326" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B327" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B328" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B329" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B330" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B331" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B332" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B333" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B334" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B335" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B336" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B337" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B338" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B339" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B340" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B341" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B342" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B343" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B344" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B345" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B346" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B347" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B348" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B349" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B350" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B351" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B352" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B353" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B354" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B355" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B356" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B357" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B358" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B359" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B360" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B361" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B362" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B363" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B364" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B365" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B366" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B367" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B368" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B369" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B370" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B371" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B372" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B373" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B374" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B375" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B376" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B377" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B378" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B379" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B380" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B381" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B382" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B383" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B384" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B385" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B386" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B387" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B388" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B389" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B390" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B391" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B392" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B393" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B394" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B395" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B396" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B397" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B398" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B399" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B400" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B401" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B402" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B403" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B404" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B405" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B406" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B407" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B408" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B409" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B410" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B411" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B412" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B413" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B414" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B415" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B416" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B417" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B418" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B419" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B420" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B421" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B422" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B423" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B424" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B425" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B426" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B427" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B428" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B429" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B430" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B431" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B432" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B433" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B434" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B435" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B436" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B437" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B438" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B439" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B440" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B441" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B442" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B443" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B444" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B445" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B446" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B447" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B448" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B449" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B450" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B451" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B452" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B453" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B454" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B455" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B456" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B457" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B458" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B459" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B460" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B461" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B462" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B463" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B464" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B465" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B466" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B467" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B468" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B469" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B470" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B471" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B472" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B473" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B474" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B475" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B476" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B477" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B478" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B479" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B480" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B481" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B482" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B483" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B484" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B485" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B486" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B487" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B488" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B489" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B490" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B491" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B492" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B493" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B494" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B495" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B496" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B497" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B498" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B499" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B500" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B501" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B502" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B503" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B504" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B505" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B506" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B507" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B508" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B509" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B510" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B511" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B512" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B513" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B514" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B515" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B516" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B517" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B518" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B519" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B520" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B521" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B522" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B523" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B524" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B525" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B526" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B527" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B528" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B529" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B530" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B531" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B532" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B533" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B534" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B535" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B536" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B537" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B538" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B539" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B540" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B541" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B542" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B543" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B544" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B545" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B546" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B547" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B548" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B549" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B550" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B551" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B552" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B553" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B554" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B555" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B556" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B557" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B558" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B559" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B560" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B561" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B562" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B563" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B564" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B565" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B566" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B567" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B568" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B569" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B570" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B571" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B572" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B573" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B574" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B575" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B576" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B577" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B578" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B579" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B580" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B581" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B582" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B583" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B584" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B585" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B586" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B587" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B588" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B589" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B590" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B591" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B592" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B593" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B594" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B595" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B596" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B597" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B598" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B599" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B600" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B601" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B602" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B603" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B604" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B605" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B606" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B607" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B608" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B609" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B610" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B611" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B612" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B613" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B614" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B615" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B616" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B617" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B618" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B619" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B620" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B621" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B622" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B623" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B624" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B625" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B626" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B627" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B628" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B629" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B630" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B631" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B632" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B633" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B634" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B635" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B636" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B637" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B638" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B639" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B640" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B641" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B642" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B643" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B644" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B645" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B646" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B647" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B648" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B649" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B650" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B651" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B652" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B653" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B654" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B655" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B656" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B657" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B658" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B659" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B660" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B661" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B662" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B663" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B664" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B665" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B666" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B667" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B668" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B669" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B670" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B671" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B672" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B673" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B674" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B675" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B676" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B677" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B678" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B679" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B680" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B681" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B682" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B683" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B684" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B685" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B686" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B687" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B688" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B689" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B690" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B691" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B692" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B693" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B694" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B695" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B696" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B697" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B698" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B699" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B700" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B701" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B702" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B703" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B704" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B705" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B706" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B707" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B708" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B709" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B710" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B711" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B712" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B713" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B714" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B715" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B716" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B717" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B718" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B719" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B720" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B721" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B722" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B723" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B724" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B725" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B726" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B727" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B728" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B729" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B730" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B731" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B732" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B733" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B734" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B735" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B736" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B737" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B738" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B739" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B740" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B741" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B742" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B743" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B744" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B745" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B746" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B747" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B748" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B749" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B750" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B751" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B752" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B753" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B754" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B755" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B756" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B757" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B758" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B759" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B760" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B761" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B762" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B763" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B764" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B765" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B766" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B767" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B768" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B769" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B770" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B771" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B772" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B773" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B774" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B775" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B776" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B777" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B778" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B779" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B780" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B781" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B782" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B783" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B784" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B785" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B786" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B787" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B788" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B789" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B790" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B791" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B792" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B793" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B794" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B795" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B796" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B797" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B798" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B799" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B800" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B801" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B802" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B803" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B804" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B805" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B806" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B807" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B808" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B809" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B810" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B811" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B812" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B813" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B814" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B815" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B816" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B817" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B818" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B819" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B820" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B821" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B822" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B823" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B824" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B825" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B826" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B827" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B828" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B829" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B830" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B831" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B832" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B833" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B834" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B835" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B836" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B837" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B838" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B839" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B840" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B841" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B842" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B843" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B844" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B845" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B846" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B847" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B848" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B849" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B850" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B851" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B852" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B853" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B854" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B855" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B856" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B857" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B858" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B859" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B860" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B861" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B862" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B863" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B864" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B865" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B866" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B867" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B868" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B869" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B870" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B871" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B872" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B873" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B874" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B875" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B876" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B877" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B878" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B879" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B880" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B881" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B882" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B883" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B884" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B885" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B886" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B887" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B888" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B889" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B890" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B891" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B892" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B893" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B894" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B895" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B896" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B897" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B898" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B899" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B900" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B901" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B902" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B903" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B904" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B905" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B906" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B907" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B908" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B909" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B910" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B911" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B912" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B913" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B914" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B915" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B916" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B917" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B918" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B919" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B920" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B921" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B922" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B923" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B924" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B925" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B926" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B927" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B928" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B929" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B930" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B931" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B932" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B933" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B934" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B935" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B936" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B937" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B938" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B939" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B940" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B941" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B942" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B943" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B944" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B945" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B946" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B947" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B948" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B949" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B950" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B951" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B952" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B953" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B954" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B955" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B956" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B957" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B958" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B959" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B960" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B961" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B962" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B963" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B964" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B965" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B966" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B967" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B968" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B969" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B970" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B971" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B972" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B973" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B974" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B975" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B976" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B977" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B978" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B979" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B980" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B981" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B982" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B983" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B984" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B985" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B986" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B987" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B988" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B989" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B990" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B991" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B992" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B993" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B994" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B995" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B996" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B997" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B998" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B999" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1000" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1001" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1002" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1003" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1004" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1005" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1006" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1007" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1008" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1009" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1010" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1011" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1012" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1013" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1014" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1015" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1016" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1017" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1018" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1019" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1020" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1021" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1022" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1023" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1024" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1025" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1026" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1027" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1028" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1029" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1030" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1031" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1032" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1033" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1034" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1035" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1036" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1037" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1038" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1039" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1040" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1041" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1042" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1043" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1044" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1045" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1046" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1047" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1048" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1049" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1050" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1051" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1052" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1053" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1054" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1055" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1056" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1057" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1058" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1059" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1060" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1061" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1062" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1063" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1064" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1065" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1066" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1067" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1068" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1069" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1070" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1071" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1072" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1073" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1074" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1075" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1076" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1077" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1078" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1079" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1080" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1081" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1082" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1083" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1084" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1085" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1086" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1087" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1088" r:id="rId1082"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45749,6 +46839,38 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
